--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_SCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_SCP.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'context_alerts'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'team_splits'!$A$1:$I$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>79.5</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>72.0</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>7.5</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,11 @@
           <t>diff_casa</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>28.0</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -642,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q2 (3)</t>
+          <t>Q2 (9)</t>
         </is>
       </c>
     </row>
@@ -659,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q4 (-10)</t>
+          <t>Q4 (-2.5)</t>
         </is>
       </c>
     </row>
@@ -675,11 +679,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -697,29 +701,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>períodos</t>
+          <t>home/away</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Melhor período: Q2 (3)</t>
+          <t>Diff médio casa: 28 | fora: -13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>resultado</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Diff médio em vitórias: 28 | em derrotas: -13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>períodos</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Pior período: Q4 (-10)</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Melhor período: Q2 (9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>períodos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pior período: Q4 (-2.5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>player swing</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>G. Kalscheur sobe mais em vitórias (12 ppg).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B3"/>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -730,7 +770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -824,8 +864,41 @@
         <v>-13</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>88</v>
+      </c>
+      <c r="E3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F3" t="n">
+        <v>28</v>
+      </c>
+      <c r="G3" t="n">
+        <v>88</v>
+      </c>
+      <c r="H3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I3" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:I3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -924,31 +997,45 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>G. Kalscheur</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>21</v>
+      </c>
       <c r="E2" t="n">
-        <v>32.5</v>
+        <v>22.9</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>-11</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>17</v>
+      </c>
+      <c r="I2" t="n">
+        <v>21</v>
+      </c>
       <c r="J2" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>-11</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+        <v>-1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>12</v>
+      </c>
+      <c r="M2" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -956,9 +1043,15 @@
           <t>A. Cruz</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="B3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>18</v>
+      </c>
       <c r="E3" t="n">
         <v>14</v>
       </c>
@@ -968,132 +1061,196 @@
       <c r="G3" t="n">
         <v>-12</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>18</v>
+      </c>
       <c r="J3" t="n">
         <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>-12</v>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. Ventura</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>T. Baskin</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>21</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>18</v>
+      </c>
       <c r="E4" t="n">
-        <v>22.7</v>
+        <v>16.3</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>-14</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>18</v>
+      </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>-14</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>J. Embalo</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
       <c r="E5" t="n">
-        <v>31.3</v>
+        <v>20.2</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-8</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>-9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7</v>
+      </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>-9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>D. Ventura</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16</v>
+      </c>
       <c r="E6" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>-14</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>16</v>
+      </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+        <v>-14</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. Embalo</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>F. Amarante</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
       <c r="E7" t="n">
-        <v>20.2</v>
+        <v>31.3</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>-9</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+        <v>-8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+        <v>-8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1101,9 +1258,15 @@
           <t>J. Fernandes</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
       <c r="E8" t="n">
         <v>15.3</v>
       </c>
@@ -1113,45 +1276,67 @@
       <c r="G8" t="n">
         <v>-5</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
       <c r="J8" t="n">
         <v>4</v>
       </c>
       <c r="K8" t="n">
         <v>-5</v>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>Liam Reilly</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="C9" t="n">
+        <v>13</v>
+      </c>
+      <c r="D9" t="n">
+        <v>14</v>
+      </c>
       <c r="E9" t="n">
-        <v>16.3</v>
+        <v>32.5</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+        <v>-11</v>
+      </c>
+      <c r="H9" t="n">
+        <v>13</v>
+      </c>
+      <c r="I9" t="n">
+        <v>14</v>
+      </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+        <v>-11</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-13</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-13</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M9"/>
@@ -1260,25 +1445,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="J2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
@@ -1303,25 +1488,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I3" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="J3" t="n">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -1346,25 +1531,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="H4" t="n">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="K4" t="n">
-        <v>-6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="5">
@@ -1389,25 +1574,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="H5" t="n">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="I5" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="J5" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>-10</v>
+        <v>-2.5</v>
       </c>
     </row>
   </sheetData>
@@ -1534,23 +1719,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Liam Reilly</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>8.5</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1559,10 +1744,10 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1574,7 +1759,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1583,155 +1768,161 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. Ventura</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>T. Baskin</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.5</v>
+      </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5</v>
+      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
@@ -1739,51 +1930,53 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
+          <t>D. Ventura</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1792,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1801,27 +1994,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. Fernandes</t>
+          <t>A. Cruz</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
@@ -1835,10 +2028,10 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1848,41 +2041,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. Cruz</t>
+          <t>J. Fernandes</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C8" t="n">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1891,9 +2100,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
@@ -1901,11 +2112,13 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.5</v>
+      </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1913,9 +2126,11 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>0.5</v>
+      </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1923,7 +2138,9 @@
       <c r="N9" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
@@ -1943,11 +2160,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -2021,8 +2238,37 @@
         <v>-13</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2922725</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Esgueira Aveiro OLI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>88</v>
+      </c>
+      <c r="F3" t="n">
+        <v>60</v>
+      </c>
+      <c r="G3" t="n">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G2"/>
+  <autoFilter ref="A1:G3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_SCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_SCP.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>82.8</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.2</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>8.5</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-13.0</t>
+          <t>-11.0</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q2 (9)</t>
+          <t>Q2 (4)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Q4 (-2.5)</t>
+          <t>Q3 (-2)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio casa: 28 | fora: -13</t>
+          <t>Diff médio casa: 28 | fora: -11</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diff médio em vitórias: 28 | em derrotas: -13</t>
+          <t>Diff médio em vitórias: 28 | em derrotas: -11</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Melhor período: Q2 (9)</t>
+          <t>Melhor período: Q2 (4)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pior período: Q4 (-2.5)</t>
+          <t>Pior período: Q3 (-2)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G. Kalscheur sobe mais em vitórias (12 ppg).</t>
+          <t>B. Carter sobe mais em vitórias (9.5 ppg).</t>
         </is>
       </c>
     </row>
@@ -843,25 +843,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>71</v>
+        <v>155</v>
       </c>
       <c r="E2" t="n">
-        <v>84</v>
+        <v>177</v>
       </c>
       <c r="F2" t="n">
-        <v>-13</v>
+        <v>-22</v>
       </c>
       <c r="G2" t="n">
-        <v>71</v>
+        <v>77.5</v>
       </c>
       <c r="H2" t="n">
-        <v>84</v>
+        <v>88.5</v>
       </c>
       <c r="I2" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="3">
@@ -1010,13 +1010,13 @@
         <v>21</v>
       </c>
       <c r="E2" t="n">
-        <v>22.9</v>
+        <v>20.8</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="G2" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="H2" t="n">
         <v>17</v>
@@ -1025,59 +1025,59 @@
         <v>21</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="K2" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="L2" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="M2" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. Cruz</t>
+          <t>J. Embalo</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.5</v>
+        <v>16.9</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>20.4</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1096,13 +1096,13 @@
         <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>16.3</v>
+        <v>13.7</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>8</v>
@@ -1111,59 +1111,59 @@
         <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. Embalo</t>
+          <t>J. Fernandes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.9</v>
+        <v>16.2</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>20.2</v>
+        <v>13.5</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>-9</v>
+        <v>-1.5</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>-9</v>
+        <v>-1.5</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1182,13 +1182,13 @@
         <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>22.7</v>
+        <v>25.3</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="G6" t="n">
-        <v>-14</v>
+        <v>-5.5</v>
       </c>
       <c r="H6" t="n">
         <v>6</v>
@@ -1197,16 +1197,16 @@
         <v>16</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="K6" t="n">
-        <v>-14</v>
+        <v>-5.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="7">
@@ -1225,13 +1225,13 @@
         <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>31.3</v>
+        <v>30.2</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="H7" t="n">
         <v>8</v>
@@ -1240,59 +1240,59 @@
         <v>5</v>
       </c>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="L7" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="M7" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. Fernandes</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.2</v>
+        <v>15.4</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H8" t="n">
         <v>6</v>
       </c>
-      <c r="E8" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="F8" t="n">
-        <v>4</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>13.5</v>
       </c>
       <c r="K8" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L8" t="n">
-        <v>-1</v>
+        <v>-7.5</v>
       </c>
       <c r="M8" t="n">
-        <v>-1</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="9">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G2" t="n">
+        <v>59</v>
+      </c>
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="n">
-        <v>39</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
       <c r="I2" t="n">
-        <v>19.5</v>
+        <v>20.3</v>
       </c>
       <c r="J2" t="n">
-        <v>18</v>
+        <v>19.7</v>
       </c>
       <c r="K2" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
@@ -1488,25 +1488,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>22.5</v>
+        <v>21.7</v>
       </c>
       <c r="J3" t="n">
-        <v>13.5</v>
+        <v>17.7</v>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1531,25 +1531,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="H4" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>18.7</v>
       </c>
       <c r="J4" t="n">
-        <v>18.5</v>
+        <v>20.7</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="5">
@@ -1574,25 +1574,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="G5" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="H5" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="I5" t="n">
-        <v>19.5</v>
+        <v>20.3</v>
       </c>
       <c r="J5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.5</v>
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5</v>
+        <v>5.7</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -1744,22 +1744,22 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1768,90 +1768,90 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1869,59 +1869,59 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="D5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="G5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -1930,54 +1930,54 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. Ventura</t>
+          <t>T. Baskin</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>0.5</v>
       </c>
-      <c r="K6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
@@ -1985,58 +1985,66 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. Cruz</t>
+          <t>D. Ventura</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>1.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.3</v>
+      </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>2.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.3</v>
+      </c>
       <c r="J7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
+        <v>2.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2045,31 +2053,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="G8" t="n">
         <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -2087,7 +2095,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2100,7 +2108,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -2112,25 +2120,25 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.5</v>
       </c>
-      <c r="H9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -2160,7 +2168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2267,8 +2275,37 @@
         <v>28</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2922730</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CAB Madeira</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>84</v>
+      </c>
+      <c r="F4" t="n">
+        <v>93</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-9</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_SCP.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/context_packs/context_pack_SCP.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'key_players_context'!$A$1:$M$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'team_periods'!$A$1:$K$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'key_players_periods'!$A$1:$Q$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'game_log'!$A$1:$G$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -544,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>78.5</t>
         </is>
       </c>
     </row>
@@ -578,7 +578,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>76.8</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>1.8</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>14.5</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Q2 (4)</t>
+          <t>Q2 (5.5)</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Diff médio casa: 28 | fora: -11</t>
+          <t>Diff médio casa: 14.5 | fora: -11</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diff médio em vitórias: 28 | em derrotas: -11</t>
+          <t>Diff médio em vitórias: 14.5 | em derrotas: -11</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Melhor período: Q2 (4)</t>
+          <t>Melhor período: Q2 (5.5)</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>B. Carter sobe mais em vitórias (9.5 ppg).</t>
+          <t>G. Kalscheur sobe mais em vitórias (8 ppg).</t>
         </is>
       </c>
     </row>
@@ -876,25 +876,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>88</v>
+        <v>79.5</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I3" t="n">
-        <v>28</v>
+        <v>14.5</v>
       </c>
     </row>
   </sheetData>
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
         <v>20.8</v>
@@ -1019,10 +1019,10 @@
         <v>-4</v>
       </c>
       <c r="H2" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="I2" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
         <v>7.5</v>
@@ -1031,10 +1031,10 @@
         <v>-4</v>
       </c>
       <c r="L2" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.9</v>
+        <v>18.8</v>
       </c>
       <c r="C3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D3" t="n">
         <v>3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>20.4</v>
@@ -1062,10 +1062,10 @@
         <v>-11</v>
       </c>
       <c r="H3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I3" t="n">
         <v>3</v>
-      </c>
-      <c r="I3" t="n">
-        <v>7</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -1074,53 +1074,53 @@
         <v>-11</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
+          <t>D. Ventura</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>25.5</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>10.5</v>
       </c>
       <c r="E4" t="n">
-        <v>13.7</v>
+        <v>25.3</v>
       </c>
       <c r="F4" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="G4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
-        <v>8</v>
-      </c>
-      <c r="I4" t="n">
-        <v>18</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -1130,13 +1130,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.2</v>
+        <v>13.8</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="E5" t="n">
         <v>13.5</v>
@@ -1148,10 +1148,10 @@
         <v>-1.5</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
@@ -1160,47 +1160,47 @@
         <v>-1.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. Ventura</t>
+          <t>T. Baskin</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.6</v>
+        <v>10.8</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>25.3</v>
+        <v>13.7</v>
       </c>
       <c r="F6" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.5</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.5</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>-2.5</v>
@@ -1216,13 +1216,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17.4</v>
+        <v>21.9</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>30.2</v>
@@ -1234,10 +1234,10 @@
         <v>-4</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>13</v>
@@ -1246,10 +1246,10 @@
         <v>-4</v>
       </c>
       <c r="L7" t="n">
-        <v>-5</v>
+        <v>-3.5</v>
       </c>
       <c r="M7" t="n">
-        <v>-5</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="8">
@@ -1259,13 +1259,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.4</v>
+        <v>18.2</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="E8" t="n">
         <v>21.1</v>
@@ -1277,10 +1277,10 @@
         <v>-3</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="J8" t="n">
         <v>13.5</v>
@@ -1289,10 +1289,10 @@
         <v>-3</v>
       </c>
       <c r="L8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
       <c r="M8" t="n">
-        <v>-7.5</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="9">
@@ -1302,40 +1302,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16.1</v>
+        <v>20.9</v>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>32.5</v>
+        <v>27.1</v>
       </c>
       <c r="F9" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="G9" t="n">
-        <v>-11</v>
+        <v>-7.5</v>
       </c>
       <c r="H9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="K9" t="n">
-        <v>-11</v>
+        <v>-7.5</v>
       </c>
       <c r="L9" t="n">
-        <v>-13</v>
+        <v>-8.5</v>
       </c>
       <c r="M9" t="n">
-        <v>-13</v>
+        <v>-8.5</v>
       </c>
     </row>
   </sheetData>
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="G2" t="n">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="I2" t="n">
-        <v>20.3</v>
+        <v>19.2</v>
       </c>
       <c r="J2" t="n">
-        <v>19.7</v>
+        <v>20.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="3">
@@ -1488,25 +1488,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
+        <v>87</v>
+      </c>
+      <c r="G3" t="n">
         <v>65</v>
       </c>
-      <c r="G3" t="n">
-        <v>53</v>
-      </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I3" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="J3" t="n">
-        <v>17.7</v>
+        <v>16.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="4">
@@ -1531,22 +1531,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="G4" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="H4" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="I4" t="n">
-        <v>18.7</v>
+        <v>17.5</v>
       </c>
       <c r="J4" t="n">
-        <v>20.7</v>
+        <v>19.5</v>
       </c>
       <c r="K4" t="n">
         <v>-2</v>
@@ -1574,25 +1574,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="G5" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="H5" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="I5" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
-        <v>21</v>
+        <v>20.2</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7</v>
+        <v>-0.2</v>
       </c>
     </row>
   </sheetData>
@@ -1723,44 +1723,44 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C2" t="n">
         <v>4</v>
       </c>
-      <c r="C2" t="n">
-        <v>4.3</v>
-      </c>
       <c r="D2" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.3</v>
-      </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
@@ -1768,270 +1768,270 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>F. Amarante</t>
+          <t>J. Davis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="I3" t="n">
         <v>1.7</v>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0.3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. Davis</t>
+          <t>G. Kalscheur</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="C4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="D4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.5</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.7</v>
-      </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. Kalscheur</t>
+          <t>F. Amarante</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="F5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="L5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. Baskin</t>
+          <t>D. Ventura</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="C6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="D6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. Ventura</t>
+          <t>T. Baskin</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F7" t="n">
         <v>1.3</v>
       </c>
-      <c r="E7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
       <c r="G7" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
         <v>0.3</v>
       </c>
-      <c r="J7" t="n">
-        <v>0.7</v>
-      </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -2040,10 +2040,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -2053,35 +2053,35 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="E8" t="n">
         <v>0.3</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="I8" t="n">
         <v>0.7</v>
       </c>
       <c r="J8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K8" t="n">
         <v>0.7</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -2108,43 +2108,43 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G9" t="n">
         <v>1</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.7</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L9" t="n">
         <v>0.5</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.3</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -2168,7 +2168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2304,8 +2304,37 @@
         <v>-9</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2922736</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AD Ovarense</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>71</v>
+      </c>
+      <c r="F5" t="n">
+        <v>70</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>